--- a/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_grids\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4E4D5C-59BA-4355-B176-0AE9FC80271D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1612BBA0-5BB4-4A47-BC9E-307D0A4B968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17373" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17374" uniqueCount="321">
   <si>
     <t>C1</t>
   </si>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>dem_agriculture,dem_commercial,dem_industry,dem_residential</t>
+  </si>
+  <si>
+    <t>12,15</t>
   </si>
 </sst>
 </file>
@@ -6295,103 +6298,16 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.45">
       <c r="G1" s="18" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,G1:EE1)</f>
-        <v>~Inputcell: 22,25</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-      <c r="L2">
-        <v>11</v>
-      </c>
-      <c r="M2">
-        <v>16</v>
-      </c>
-      <c r="N2">
-        <v>17</v>
-      </c>
-      <c r="O2">
-        <v>18</v>
-      </c>
-      <c r="P2">
-        <v>20</v>
-      </c>
-      <c r="Q2">
-        <v>21</v>
-      </c>
-      <c r="R2">
-        <v>22</v>
-      </c>
-      <c r="S2">
-        <v>27</v>
-      </c>
-      <c r="T2">
-        <v>28</v>
-      </c>
-      <c r="U2">
-        <v>29</v>
-      </c>
-      <c r="V2">
-        <v>31</v>
-      </c>
-      <c r="W2">
-        <v>32</v>
-      </c>
-      <c r="X2">
-        <v>33</v>
-      </c>
-      <c r="Y2">
-        <v>38</v>
-      </c>
-      <c r="Z2">
-        <v>39</v>
-      </c>
-      <c r="AA2">
-        <v>40</v>
-      </c>
-      <c r="AB2">
-        <v>42</v>
-      </c>
-      <c r="AC2">
-        <v>43</v>
-      </c>
-      <c r="AD2">
-        <v>44</v>
-      </c>
-      <c r="AE2">
-        <v>49</v>
-      </c>
-      <c r="AF2">
-        <v>50</v>
-      </c>
-      <c r="AG2">
-        <v>51</v>
-      </c>
-      <c r="AH2">
-        <v>53</v>
-      </c>
-      <c r="AI2">
-        <v>54</v>
-      </c>
-      <c r="AJ2">
-        <v>55</v>
+        <v>~Inputcell: 12,15</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.45">

--- a/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1612BBA0-5BB4-4A47-BC9E-307D0A4B968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8179F72D-F006-48E1-B722-610C8D57E947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -6312,13 +6312,13 @@
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(D3,$C$9:$E$999,2,FALSE)</f>
-        <v>ts_048</v>
+        <v>ts_012</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>VLOOKUP(D3,$C$9:$E$999,3,FALSE)</f>
@@ -24413,7 +24413,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>IFERROR(Veda!D5,"ts_12t")</f>
-        <v>ts_048</v>
+        <v>ts_012</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15" t="s">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S03aH05,S05aH05,S02aH01,S05aH06,S01aH05,S03aH06,S06aH05,S05aH01,S07aH06,S08aH01,S08aH05,S04aH05,S06aH01,S06aH06,S01aH06,S07aH01,S08aH06,S03aH01,S01aH01,S04aH01,S04aH06,S02aH05,S07aH05</v>
+        <v>S03aH01,S03aH03,S01aH01,S04aH01,S04aH03,S01aH03,S02aH01,S02aH03</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S04aH03,S07aH04,S08aH03,S01aH02,S04aH04,S03aH04,S01aH04,S07aH02,S08aH02,S03aH03,S05aH04,S06aH02,S06aH03,S01aH03,S05aH02,S05aH03,S02aH02,S03aH02,S02aH03,S07aH03,S06aH04,S08aH04,S04aH02</v>
+        <v>S02aH02,S03aH02,S01aH02,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -24618,35 +24618,35 @@
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>DeActivated</v>
+        <v>~TimeSlices</v>
       </c>
       <c r="I9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="N9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="S9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="X9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="AC9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="AG9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="AK9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>DeActivated</v>
+        <v>~TFM_INS-AT</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.45">
@@ -24714,10 +24714,10 @@
         <v>123</v>
       </c>
       <c r="AA10" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="AC10" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="AD10" t="s">
         <v>123</v>
@@ -24750,7 +24750,7 @@
     <row r="11" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>x</v>
+        <v>ok</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -24813,10 +24813,10 @@
         <v>161</v>
       </c>
       <c r="AA11" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC11" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD11" t="s">
         <v>161</v>
@@ -24902,10 +24902,10 @@
         <v>163</v>
       </c>
       <c r="AA12" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC12" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD12" t="s">
         <v>163</v>
@@ -24991,10 +24991,10 @@
         <v>164</v>
       </c>
       <c r="AA13" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC13" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD13" t="s">
         <v>164</v>
@@ -25074,10 +25074,10 @@
         <v>165</v>
       </c>
       <c r="AA14" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC14" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD14" t="s">
         <v>165</v>
@@ -25154,10 +25154,10 @@
         <v>166</v>
       </c>
       <c r="AA15" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC15" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD15" t="s">
         <v>166</v>
@@ -25234,10 +25234,10 @@
         <v>167</v>
       </c>
       <c r="AA16" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC16" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD16" t="s">
         <v>167</v>
@@ -25314,10 +25314,10 @@
         <v>168</v>
       </c>
       <c r="AA17" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC17" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD17" t="s">
         <v>168</v>
@@ -25394,10 +25394,10 @@
         <v>169</v>
       </c>
       <c r="AA18" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC18" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD18" t="s">
         <v>169</v>
@@ -25474,10 +25474,10 @@
         <v>170</v>
       </c>
       <c r="AA19" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC19" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD19" t="s">
         <v>170</v>
@@ -25554,10 +25554,10 @@
         <v>171</v>
       </c>
       <c r="AA20" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC20" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD20" t="s">
         <v>171</v>
@@ -25634,10 +25634,10 @@
         <v>172</v>
       </c>
       <c r="AA21" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC21" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD21" t="s">
         <v>172</v>
@@ -25714,10 +25714,10 @@
         <v>173</v>
       </c>
       <c r="AA22" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="AC22" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="AD22" t="s">
         <v>173</v>
@@ -25785,7 +25785,7 @@
         <v>162</v>
       </c>
       <c r="AC23" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD23" t="s">
         <v>161</v>
@@ -25844,7 +25844,7 @@
         <v>162</v>
       </c>
       <c r="AC24" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD24" t="s">
         <v>163</v>
@@ -25903,7 +25903,7 @@
         <v>162</v>
       </c>
       <c r="AC25" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD25" t="s">
         <v>164</v>
@@ -25962,7 +25962,7 @@
         <v>162</v>
       </c>
       <c r="AC26" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD26" t="s">
         <v>165</v>
@@ -26021,7 +26021,7 @@
         <v>162</v>
       </c>
       <c r="AC27" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD27" t="s">
         <v>166</v>
@@ -26080,7 +26080,7 @@
         <v>162</v>
       </c>
       <c r="AC28" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD28" t="s">
         <v>167</v>
@@ -26139,7 +26139,7 @@
         <v>162</v>
       </c>
       <c r="AC29" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD29" t="s">
         <v>168</v>
@@ -26198,7 +26198,7 @@
         <v>162</v>
       </c>
       <c r="AC30" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD30" t="s">
         <v>169</v>
@@ -26257,7 +26257,7 @@
         <v>162</v>
       </c>
       <c r="AC31" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD31" t="s">
         <v>170</v>
@@ -26316,7 +26316,7 @@
         <v>162</v>
       </c>
       <c r="AC32" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD32" t="s">
         <v>171</v>
@@ -26375,7 +26375,7 @@
         <v>162</v>
       </c>
       <c r="AC33" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD33" t="s">
         <v>172</v>
@@ -26434,7 +26434,7 @@
         <v>162</v>
       </c>
       <c r="AC34" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AD34" t="s">
         <v>173</v>
@@ -36668,35 +36668,35 @@
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
-        <v>~TimeSlices</v>
+        <v>DeActivated</v>
       </c>
       <c r="I9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="N9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="S9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="X9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="AC9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="AG9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <v>DeActivated</v>
       </c>
       <c r="AK9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
+        <v>DeActivated</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.45">
@@ -36800,7 +36800,7 @@
     <row r="11" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>IFERROR(IF(Veda!D5=A10,"ok","x"),"")</f>
-        <v>ok</v>
+        <v>x</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>

--- a/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8179F72D-F006-48E1-B722-610C8D57E947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0931A03-D644-4E75-BD97-7296BB62EA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24633,12 +24633,12 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="X9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
+        <v>~TFM_INS-AT</v>
       </c>
       <c r="AC9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
+        <v>~TFM_INS-AT</v>
       </c>
       <c r="AG9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
